--- a/08_tables/q7_twfe_country_correlations_i_LS.xlsx
+++ b/08_tables/q7_twfe_country_correlations_i_LS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,16 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>std_twfe_LS</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>std_twfe_i</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>simple_slope</t>
         </is>
       </c>
@@ -463,7 +473,13 @@
         <v>0.5843878752776019</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8373543804952331</v>
+        <v>2.318213332948363</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.617876248859742</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8373543804952335</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +495,13 @@
         <v>0.4796868568595204</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4778646856948364</v>
+        <v>2.171745934495637</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.180027134042958</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4778646856948366</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +517,13 @@
         <v>0.4152058736231807</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6627410574185234</v>
+        <v>2.430031241068674</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.522409443455344</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6627410574185235</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +539,13 @@
         <v>0.3689251987654661</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2424446641801581</v>
+        <v>1.668117755779556</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.538355202397322</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.242444664180158</v>
       </c>
     </row>
     <row r="6">
@@ -527,6 +561,12 @@
         <v>0.2359024432482654</v>
       </c>
       <c r="D6" t="n">
+        <v>2.441015882395916</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.974052946994679</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.2917052511391273</v>
       </c>
     </row>
@@ -543,7 +583,13 @@
         <v>0.1864719104597827</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09809357656817036</v>
+        <v>1.278923994909921</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.431182642198552</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.09809357656817035</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +605,13 @@
         <v>0.1777081084621944</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2224417850062921</v>
+        <v>1.832622727124982</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.464077076854049</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2224417850062919</v>
       </c>
     </row>
     <row r="9">
@@ -575,6 +627,12 @@
         <v>0.1248192927690292</v>
       </c>
       <c r="D9" t="n">
+        <v>2.921498067419213</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.466092157962786</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.2487287859912337</v>
       </c>
     </row>
@@ -591,7 +649,13 @@
         <v>0.1175306650665298</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3568310000170072</v>
+        <v>2.937890388957019</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9676631550796512</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3568310000170073</v>
       </c>
     </row>
     <row r="11">
@@ -607,6 +671,12 @@
         <v>0.06451535393105778</v>
       </c>
       <c r="D11" t="n">
+        <v>1.437370431297379</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.905462521904596</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.04866664184635724</v>
       </c>
     </row>
@@ -623,7 +693,13 @@
         <v>-0.02113118234055538</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03360581447433966</v>
+        <v>2.010226608182081</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.264021291189566</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.03360581447433959</v>
       </c>
     </row>
     <row r="13">
@@ -639,6 +715,12 @@
         <v>-0.1193867967532351</v>
       </c>
       <c r="D13" t="n">
+        <v>1.46974698698368</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9237158829327381</v>
+      </c>
+      <c r="F13" t="n">
         <v>-0.189959259178915</v>
       </c>
     </row>
@@ -655,7 +737,13 @@
         <v>-0.2815675730156755</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4790808012242177</v>
+        <v>6.151909224747851</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.615628397962685</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.4790808012242179</v>
       </c>
     </row>
     <row r="15">
@@ -671,6 +759,12 @@
         <v>-0.47433245651632</v>
       </c>
       <c r="D15" t="n">
+        <v>1.208114906988624</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.883554235334497</v>
+      </c>
+      <c r="F15" t="n">
         <v>-0.3042376486091111</v>
       </c>
     </row>

--- a/08_tables/q7_twfe_country_correlations_i_LS.xlsx
+++ b/08_tables/q7_twfe_country_correlations_i_LS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,10 +498,10 @@
         <v>2.171745934495637</v>
       </c>
       <c r="E3" t="n">
-        <v>2.180027134042958</v>
+        <v>2.180027134042959</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4778646856948366</v>
+        <v>0.4778646856948365</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
         <v>1.522409443455344</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6627410574185235</v>
+        <v>0.6627410574185234</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>2.538355202397322</v>
       </c>
       <c r="F5" t="n">
-        <v>0.242444664180158</v>
+        <v>0.2424446641801581</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         <v>0.2359024432482654</v>
       </c>
       <c r="D6" t="n">
-        <v>2.441015882395916</v>
+        <v>2.441015882395917</v>
       </c>
       <c r="E6" t="n">
         <v>1.974052946994679</v>
@@ -602,10 +602,10 @@
         <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1777081084621944</v>
+        <v>0.1777081084621943</v>
       </c>
       <c r="D8" t="n">
-        <v>1.832622727124982</v>
+        <v>1.832622727124983</v>
       </c>
       <c r="E8" t="n">
         <v>1.464077076854049</v>
@@ -655,7 +655,7 @@
         <v>0.9676631550796512</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3568310000170073</v>
+        <v>0.3568310000170072</v>
       </c>
     </row>
     <row r="11">
@@ -668,7 +668,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06451535393105778</v>
+        <v>0.06451535393105784</v>
       </c>
       <c r="D11" t="n">
         <v>1.437370431297379</v>
@@ -677,7 +677,7 @@
         <v>1.905462521904596</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04866664184635724</v>
+        <v>0.04866664184635729</v>
       </c>
     </row>
     <row r="12">
@@ -690,7 +690,7 @@
         <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.02113118234055538</v>
+        <v>-0.02113118234055541</v>
       </c>
       <c r="D12" t="n">
         <v>2.010226608182081</v>
@@ -699,7 +699,7 @@
         <v>1.264021291189566</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.03360581447433959</v>
+        <v>-0.03360581447433964</v>
       </c>
     </row>
     <row r="13">
@@ -718,7 +718,7 @@
         <v>1.46974698698368</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9237158829327381</v>
+        <v>0.9237158829327383</v>
       </c>
       <c r="F13" t="n">
         <v>-0.189959259178915</v>
@@ -737,10 +737,10 @@
         <v>-0.2815675730156755</v>
       </c>
       <c r="D14" t="n">
-        <v>6.151909224747851</v>
+        <v>6.15190922474785</v>
       </c>
       <c r="E14" t="n">
-        <v>3.615628397962685</v>
+        <v>3.615628397962684</v>
       </c>
       <c r="F14" t="n">
         <v>-0.4790808012242179</v>
@@ -756,13 +756,13 @@
         <v>50</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.47433245651632</v>
+        <v>-0.4743324565163199</v>
       </c>
       <c r="D15" t="n">
         <v>1.208114906988624</v>
       </c>
       <c r="E15" t="n">
-        <v>1.883554235334497</v>
+        <v>1.883554235334496</v>
       </c>
       <c r="F15" t="n">
         <v>-0.3042376486091111</v>

--- a/08_tables/q7_twfe_country_correlations_i_LS.xlsx
+++ b/08_tables/q7_twfe_country_correlations_i_LS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q7_twfe_country_correlations_i_LS.xlsx
+++ b/08_tables/q7_twfe_country_correlations_i_LS.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>correlation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>std_twfe_LS</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>std_twfe_i</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>simple_slope</t>
         </is>
@@ -470,7 +458,7 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5843878752776019</v>
+        <v>0.5843878752776018</v>
       </c>
       <c r="D2" t="n">
         <v>2.318213332948363</v>
@@ -479,7 +467,7 @@
         <v>1.617876248859742</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8373543804952335</v>
+        <v>0.8373543804952333</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +480,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4796868568595204</v>
+        <v>0.4796868568595203</v>
       </c>
       <c r="D3" t="n">
         <v>2.171745934495637</v>
@@ -514,7 +502,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4152058736231807</v>
+        <v>0.4152058736231806</v>
       </c>
       <c r="D4" t="n">
         <v>2.430031241068674</v>
@@ -558,7 +546,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2359024432482654</v>
+        <v>0.2359024432482653</v>
       </c>
       <c r="D6" t="n">
         <v>2.441015882395917</v>
@@ -580,7 +568,7 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1864719104597827</v>
+        <v>0.1864719104597828</v>
       </c>
       <c r="D7" t="n">
         <v>1.278923994909921</v>
@@ -589,7 +577,7 @@
         <v>2.431182642198552</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09809357656817035</v>
+        <v>0.09809357656817037</v>
       </c>
     </row>
     <row r="8">
@@ -602,7 +590,7 @@
         <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1777081084621943</v>
+        <v>0.1777081084621944</v>
       </c>
       <c r="D8" t="n">
         <v>1.832622727124983</v>
@@ -611,7 +599,7 @@
         <v>1.464077076854049</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2224417850062919</v>
+        <v>0.222441785006292</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +621,7 @@
         <v>1.466092157962786</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2487287859912337</v>
+        <v>0.2487287859912338</v>
       </c>
     </row>
     <row r="10">
@@ -646,7 +634,7 @@
         <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1175306650665298</v>
+        <v>0.1175306650665297</v>
       </c>
       <c r="D10" t="n">
         <v>2.937890388957019</v>
@@ -668,7 +656,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06451535393105784</v>
+        <v>0.06451535393105777</v>
       </c>
       <c r="D11" t="n">
         <v>1.437370431297379</v>
@@ -677,7 +665,7 @@
         <v>1.905462521904596</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04866664184635729</v>
+        <v>0.04866664184635723</v>
       </c>
     </row>
     <row r="12">
@@ -690,7 +678,7 @@
         <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.02113118234055541</v>
+        <v>-0.02113118234055546</v>
       </c>
       <c r="D12" t="n">
         <v>2.010226608182081</v>
@@ -699,7 +687,7 @@
         <v>1.264021291189566</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.03360581447433964</v>
+        <v>-0.03360581447433972</v>
       </c>
     </row>
     <row r="13">
@@ -712,7 +700,7 @@
         <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1193867967532351</v>
+        <v>-0.119386796753235</v>
       </c>
       <c r="D13" t="n">
         <v>1.46974698698368</v>
@@ -721,7 +709,7 @@
         <v>0.9237158829327383</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.189959259178915</v>
+        <v>-0.1899592591789149</v>
       </c>
     </row>
     <row r="14">
@@ -734,7 +722,7 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2815675730156755</v>
+        <v>-0.2815675730156753</v>
       </c>
       <c r="D14" t="n">
         <v>6.15190922474785</v>
@@ -743,7 +731,7 @@
         <v>3.615628397962684</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4790808012242179</v>
+        <v>-0.4790808012242175</v>
       </c>
     </row>
     <row r="15">
@@ -756,7 +744,7 @@
         <v>50</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4743324565163199</v>
+        <v>-0.4743324565163202</v>
       </c>
       <c r="D15" t="n">
         <v>1.208114906988624</v>
@@ -765,7 +753,7 @@
         <v>1.883554235334496</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3042376486091111</v>
+        <v>-0.3042376486091113</v>
       </c>
     </row>
   </sheetData>
